--- a/config/nibe/example/nibe_modbus-configured.xlsx
+++ b/config/nibe/example/nibe_modbus-configured.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roelle/Library/Mobile Documents/com~apple~CloudDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E809E6F-BC0F-CE43-9154-DF25ECADFDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B68D658-B73F-1747-AA8F-877EA0E3DA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="32740" windowHeight="19860" xr2:uid="{5355E7C9-A99F-6749-ABC9-C527796D3A6D}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="32740" windowHeight="19860" xr2:uid="{5355E7C9-A99F-6749-ABC9-C527796D3A6D}"/>
   </bookViews>
   <sheets>
     <sheet name="CURRENT" sheetId="5" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7279" uniqueCount="1540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7302" uniqueCount="1543">
   <si>
     <t>Titel</t>
   </si>
@@ -4640,9 +4640,6 @@
     <t>SYS</t>
   </si>
   <si>
-    <t>Enum</t>
-  </si>
-  <si>
     <t>Duplette?</t>
   </si>
   <si>
@@ -4701,6 +4698,18 @@
   </si>
   <si>
     <t>VENT</t>
+  </si>
+  <si>
+    <t>used</t>
+  </si>
+  <si>
+    <t>#discrete</t>
+  </si>
+  <si>
+    <t>Data-Conv</t>
+  </si>
+  <si>
+    <t>#0off*on</t>
   </si>
 </sst>
 </file>
@@ -4892,14 +4901,17 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="12">
     <dxf>
       <font>
-        <strike/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FFC00000"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4920,6 +4932,102 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5300,7 +5408,7 @@
         <v>1502</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>1519</v>
+        <v>1541</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>1506</v>
@@ -5388,7 +5496,7 @@
         <v>1482</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>9</v>
@@ -5501,10 +5609,10 @@
         <v>1481</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>14</v>
@@ -5546,10 +5654,10 @@
         <v>1481</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>15</v>
@@ -5591,10 +5699,10 @@
         <v>1481</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>16</v>
@@ -5639,7 +5747,7 @@
         <v>1462</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>17</v>
@@ -5684,7 +5792,7 @@
         <v>1462</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>18</v>
@@ -5763,7 +5871,7 @@
         <v>1482</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>20</v>
@@ -5845,7 +5953,7 @@
         <v>1465</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>22</v>
@@ -5890,7 +5998,7 @@
         <v>1465</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>23</v>
@@ -6344,7 +6452,7 @@
         <v>1463</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>27</v>
@@ -6457,10 +6565,10 @@
         <v>1481</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>30</v>
@@ -8123,7 +8231,7 @@
         <v>1465</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>77</v>
@@ -8376,6 +8484,9 @@
       <c r="F82" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G82" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="I82" s="3" t="s">
         <v>1487</v>
       </c>
@@ -8418,6 +8529,9 @@
       <c r="F83" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G83" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="I83" s="3" t="s">
         <v>1487</v>
       </c>
@@ -9639,8 +9753,11 @@
       <c r="F118" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G118" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J118" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K118" s="1" t="s">
         <v>123</v>
@@ -9676,10 +9793,10 @@
         <v>1438</v>
       </c>
       <c r="F119" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="J119" s="4" t="s">
         <v>1539</v>
-      </c>
-      <c r="J119" s="4" t="s">
-        <v>1473</v>
       </c>
       <c r="K119" s="1" t="s">
         <v>124</v>
@@ -9718,7 +9835,7 @@
         <v>1438</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>1473</v>
@@ -9760,7 +9877,7 @@
         <v>1438</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="J121" s="4" t="s">
         <v>1473</v>
@@ -9928,10 +10045,10 @@
         <v>1438</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K125" s="1" t="s">
         <v>132</v>
@@ -9970,7 +10087,7 @@
         <v>1438</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="J126" s="4" t="s">
         <v>1473</v>
@@ -11035,7 +11152,7 @@
         <v>1438</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>1473</v>
@@ -11074,7 +11191,7 @@
         <v>1438</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>1473</v>
@@ -14629,10 +14746,10 @@
         <v>1481</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K254" s="1" t="s">
         <v>262</v>
@@ -14674,10 +14791,10 @@
         <v>1481</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K255" s="1" t="s">
         <v>263</v>
@@ -14837,7 +14954,7 @@
         <v>1463</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K259" s="1" t="s">
         <v>269</v>
@@ -14879,13 +14996,13 @@
         <v>1518</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="I260" s="12" t="s">
         <v>1512</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K260" s="1" t="s">
         <v>271</v>
@@ -14927,7 +15044,7 @@
         <v>1463</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K261" s="1" t="s">
         <v>272</v>
@@ -15031,10 +15148,10 @@
         <v>1481</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G264" s="12" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="I264" s="12" t="s">
         <v>1514</v>
@@ -15401,7 +15518,7 @@
         <v>1518</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J274" s="4" t="s">
         <v>1473</v>
@@ -15480,13 +15597,13 @@
         <v>1462</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="I276" s="12" t="s">
         <v>1511</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K276" s="1" t="s">
         <v>287</v>
@@ -15567,7 +15684,7 @@
         <v>1462</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J278" s="4" t="s">
         <v>1473</v>
@@ -15609,7 +15726,7 @@
         <v>1481</v>
       </c>
       <c r="I279" s="3" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="J279" s="4" t="s">
         <v>1455</v>
@@ -15653,6 +15770,9 @@
       <c r="F280" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G280" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="I280" s="3" t="s">
         <v>1487</v>
       </c>
@@ -15695,6 +15815,9 @@
       <c r="F281" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G281" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="I281" s="3" t="s">
         <v>1487</v>
       </c>
@@ -15876,6 +15999,9 @@
       <c r="F286" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G286" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J286" s="4" t="s">
         <v>1473</v>
       </c>
@@ -15918,6 +16044,9 @@
       <c r="F287" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G287" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J287" s="4" t="s">
         <v>1473</v>
       </c>
@@ -15961,7 +16090,7 @@
         <v>1518</v>
       </c>
       <c r="I288" s="3" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="J288" s="4" t="s">
         <v>1473</v>
@@ -16005,6 +16134,9 @@
       <c r="F289" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G289" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J289" s="4" t="s">
         <v>1473</v>
       </c>
@@ -16123,10 +16255,10 @@
         <v>1518</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K292" s="1" t="s">
         <v>305</v>
@@ -16201,6 +16333,9 @@
       <c r="F294" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G294" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J294" s="4" t="s">
         <v>1473</v>
       </c>
@@ -16243,6 +16378,9 @@
       <c r="F295" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G295" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J295" s="4" t="s">
         <v>1473</v>
       </c>
@@ -16285,6 +16423,9 @@
       <c r="F296" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G296" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J296" s="4" t="s">
         <v>1473</v>
       </c>
@@ -16328,7 +16469,7 @@
         <v>1465</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K297" s="1" t="s">
         <v>310</v>
@@ -16373,7 +16514,7 @@
         <v>1465</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K298" s="1" t="s">
         <v>311</v>
@@ -16753,8 +16894,11 @@
       <c r="F307" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G307" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J307" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K307" s="1" t="s">
         <v>1440</v>
@@ -17006,7 +17150,7 @@
         <v>1516</v>
       </c>
       <c r="F314" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J314" s="4" t="s">
         <v>1473</v>
@@ -17090,7 +17234,7 @@
         <v>1516</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J316" s="4" t="s">
         <v>1473</v>
@@ -17138,7 +17282,7 @@
         <v>1482</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K317" s="1" t="s">
         <v>328</v>
@@ -17225,10 +17369,10 @@
         <v>1481</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K319" s="1" t="s">
         <v>291</v>
@@ -17496,7 +17640,7 @@
         <v>1464</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K326" s="1" t="s">
         <v>337</v>
@@ -17540,8 +17684,11 @@
       <c r="F327" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G327" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J327" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K327" s="1" t="s">
         <v>338</v>
@@ -17577,16 +17724,16 @@
         <v>1438</v>
       </c>
       <c r="F328" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G328" s="3" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="I328" s="12" t="s">
         <v>1507</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K328" s="1" t="s">
         <v>339</v>
@@ -17765,10 +17912,10 @@
         <v>1481</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="I333" s="12" t="s">
         <v>1511</v>
@@ -17883,7 +18030,7 @@
         <v>1464</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K336" s="1" t="s">
         <v>347</v>
@@ -18578,8 +18725,11 @@
       <c r="F355" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G355" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J355" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K355" s="1" t="s">
         <v>367</v>
@@ -18620,8 +18770,11 @@
       <c r="F356" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G356" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J356" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K356" s="1" t="s">
         <v>369</v>
@@ -18876,7 +19029,7 @@
         <v>1462</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K363" s="1" t="s">
         <v>730</v>
@@ -18911,11 +19064,17 @@
         <f t="shared" si="5"/>
         <v>i02147</v>
       </c>
+      <c r="D364" s="16" t="s">
+        <v>1498</v>
+      </c>
       <c r="E364" s="3" t="s">
         <v>1438</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>1518</v>
+      </c>
+      <c r="G364" s="3" t="s">
+        <v>1540</v>
       </c>
       <c r="J364" s="4" t="s">
         <v>1473</v>
@@ -19283,13 +19442,13 @@
         <v>1518</v>
       </c>
       <c r="G374" s="3" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="I374" s="12" t="s">
         <v>1513</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K374" s="1" t="s">
         <v>264</v>
@@ -19328,13 +19487,13 @@
         <v>1462</v>
       </c>
       <c r="G375" s="3" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="I375" s="12" t="s">
         <v>1508</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K375" s="1" t="s">
         <v>295</v>
@@ -19642,7 +19801,7 @@
         <v>1516</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J384" s="4" t="s">
         <v>1473</v>
@@ -19726,7 +19885,7 @@
         <v>1516</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J386" s="4" t="s">
         <v>1473</v>
@@ -19810,7 +19969,7 @@
         <v>1516</v>
       </c>
       <c r="F388" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J388" s="4" t="s">
         <v>1473</v>
@@ -22075,7 +22234,7 @@
         <v>98</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K451" s="1" t="s">
         <v>96</v>
@@ -22302,7 +22461,10 @@
         <v>1481</v>
       </c>
       <c r="F457" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
+      </c>
+      <c r="G457" s="3" t="s">
+        <v>1540</v>
       </c>
       <c r="J457" s="4" t="s">
         <v>1473</v>
@@ -22341,7 +22503,10 @@
         <v>1481</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
+      </c>
+      <c r="G458" s="3" t="s">
+        <v>1540</v>
       </c>
       <c r="J458" s="4" t="s">
         <v>1473</v>
@@ -22380,7 +22545,10 @@
         <v>1481</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
+      </c>
+      <c r="G459" s="3" t="s">
+        <v>1540</v>
       </c>
       <c r="J459" s="4" t="s">
         <v>1473</v>
@@ -22419,7 +22587,10 @@
         <v>1481</v>
       </c>
       <c r="F460" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
+      </c>
+      <c r="G460" s="3" t="s">
+        <v>1540</v>
       </c>
       <c r="J460" s="4" t="s">
         <v>1473</v>
@@ -22458,7 +22629,7 @@
         <v>1481</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="J461" s="4" t="s">
         <v>1473</v>
@@ -22500,7 +22671,7 @@
         <v>1481</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="J462" s="4" t="s">
         <v>1473</v>
@@ -22542,7 +22713,7 @@
         <v>1481</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="J463" s="4" t="s">
         <v>1473</v>
@@ -22584,7 +22755,7 @@
         <v>1481</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="J464" s="4" t="s">
         <v>1473</v>
@@ -22629,7 +22800,7 @@
         <v>1481</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J465" s="4" t="s">
         <v>1473</v>
@@ -22674,7 +22845,7 @@
         <v>1481</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J466" s="4" t="s">
         <v>1473</v>
@@ -22719,7 +22890,7 @@
         <v>1481</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J467" s="4" t="s">
         <v>1473</v>
@@ -22764,7 +22935,7 @@
         <v>1481</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J468" s="4" t="s">
         <v>1473</v>
@@ -22809,7 +22980,7 @@
         <v>1481</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J469" s="4" t="s">
         <v>1473</v>
@@ -22854,7 +23025,7 @@
         <v>1481</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J470" s="4" t="s">
         <v>1473</v>
@@ -22899,7 +23070,7 @@
         <v>1481</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J471" s="4" t="s">
         <v>1473</v>
@@ -23170,13 +23341,13 @@
         <v>1462</v>
       </c>
       <c r="G478" s="3" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="I478" s="12" t="s">
         <v>1509</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K478" s="1" t="s">
         <v>389</v>
@@ -23215,7 +23386,7 @@
         <v>1462</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K479" s="1" t="s">
         <v>390</v>
@@ -23257,7 +23428,7 @@
         <v>1462</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K480" s="1" t="s">
         <v>391</v>
@@ -23299,7 +23470,7 @@
         <v>1462</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K481" s="1" t="s">
         <v>392</v>
@@ -23383,7 +23554,7 @@
         <v>1462</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K483" s="1" t="s">
         <v>394</v>
@@ -23425,7 +23596,7 @@
         <v>1462</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K484" s="1" t="s">
         <v>395</v>
@@ -23467,7 +23638,7 @@
         <v>1462</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K485" s="1" t="s">
         <v>396</v>
@@ -23668,6 +23839,9 @@
       <c r="F490" s="3" t="s">
         <v>1518</v>
       </c>
+      <c r="G490" s="3" t="s">
+        <v>1540</v>
+      </c>
       <c r="J490" s="4" t="s">
         <v>1473</v>
       </c>
@@ -23747,7 +23921,7 @@
         <v>1481</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J492" s="4" t="s">
         <v>1473</v>
@@ -24635,10 +24809,10 @@
         <v>1481</v>
       </c>
       <c r="F515" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G515" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J515" s="4" t="s">
         <v>1473</v>
@@ -24745,7 +24919,7 @@
         <v>1481</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="J518" s="4" t="s">
         <v>1473</v>
@@ -24784,7 +24958,7 @@
         <v>1481</v>
       </c>
       <c r="F519" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="J519" s="4" t="s">
         <v>1473</v>
@@ -24976,7 +25150,7 @@
         <v>1481</v>
       </c>
       <c r="F524" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J524" s="4" t="s">
         <v>1473</v>
@@ -25265,7 +25439,7 @@
         <v>1518</v>
       </c>
       <c r="G532" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="I532" s="12" t="s">
         <v>1511</v>
@@ -25310,7 +25484,7 @@
         <v>1518</v>
       </c>
       <c r="G533" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="I533" s="12" t="s">
         <v>1511</v>
@@ -25358,7 +25532,7 @@
         <v>1518</v>
       </c>
       <c r="G534" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="I534" s="12" t="s">
         <v>1511</v>
@@ -25655,7 +25829,7 @@
         <v>1518</v>
       </c>
       <c r="G541" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J541" s="4" t="s">
         <v>1473</v>
@@ -25697,7 +25871,7 @@
         <v>1518</v>
       </c>
       <c r="G542" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J542" s="4" t="s">
         <v>1473</v>
@@ -25739,7 +25913,7 @@
         <v>1518</v>
       </c>
       <c r="G543" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J543" s="4" t="s">
         <v>1473</v>
@@ -26490,13 +26664,13 @@
         <v>1518</v>
       </c>
       <c r="G564" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="I564" s="12" t="s">
         <v>1510</v>
       </c>
       <c r="J564" s="4" t="s">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="K564" s="1" t="s">
         <v>406</v>
@@ -26650,7 +26824,7 @@
         <v>1462</v>
       </c>
       <c r="G568" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J568" s="4" t="s">
         <v>1473</v>
@@ -26773,7 +26947,7 @@
         <v>1462</v>
       </c>
       <c r="G571" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J571" s="4" t="s">
         <v>1473</v>
@@ -32063,7 +32237,7 @@
         <v>1518</v>
       </c>
       <c r="G722" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J722" s="4" t="s">
         <v>1473</v>
@@ -32108,7 +32282,7 @@
         <v>1518</v>
       </c>
       <c r="G723" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J723" s="4" t="s">
         <v>1473</v>
@@ -32357,7 +32531,7 @@
         <v>1518</v>
       </c>
       <c r="G730" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J730" s="4" t="s">
         <v>1473</v>
@@ -32402,7 +32576,7 @@
         <v>1518</v>
       </c>
       <c r="G731" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J731" s="4" t="s">
         <v>1473</v>
@@ -33739,7 +33913,7 @@
         <v>1518</v>
       </c>
       <c r="G770" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J770" s="4" t="s">
         <v>1473</v>
@@ -33784,7 +33958,7 @@
         <v>1518</v>
       </c>
       <c r="G771" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J771" s="4" t="s">
         <v>1473</v>
@@ -35121,7 +35295,7 @@
         <v>1518</v>
       </c>
       <c r="G810" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J810" s="4" t="s">
         <v>1473</v>
@@ -35166,7 +35340,7 @@
         <v>1518</v>
       </c>
       <c r="G811" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J811" s="4" t="s">
         <v>1473</v>
@@ -35415,7 +35589,7 @@
         <v>1518</v>
       </c>
       <c r="G818" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J818" s="4" t="s">
         <v>1473</v>
@@ -35460,7 +35634,7 @@
         <v>1518</v>
       </c>
       <c r="G819" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J819" s="4" t="s">
         <v>1473</v>
@@ -35709,7 +35883,7 @@
         <v>1518</v>
       </c>
       <c r="G826" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="J826" s="4" t="s">
         <v>1473</v>
@@ -39885,7 +40059,7 @@
         <v>h02742</v>
       </c>
       <c r="G940" s="14" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="J940" s="4" t="s">
         <v>1474</v>
@@ -43290,7 +43464,7 @@
         <v>1481</v>
       </c>
       <c r="F1038" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J1038" s="4" t="s">
         <v>1473</v>
@@ -43332,7 +43506,7 @@
         <v>1481</v>
       </c>
       <c r="F1039" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J1039" s="4" t="s">
         <v>1473</v>
@@ -43374,7 +43548,7 @@
         <v>1481</v>
       </c>
       <c r="F1040" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J1040" s="4" t="s">
         <v>1473</v>
@@ -44821,7 +44995,7 @@
         <v>1481</v>
       </c>
       <c r="I1081" s="3" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="J1081" s="4" t="s">
         <v>1474</v>
@@ -51403,8 +51577,8 @@
       <c r="F1270" s="3" t="s">
         <v>1518</v>
       </c>
-      <c r="G1270" s="14" t="s">
-        <v>1527</v>
+      <c r="G1270" s="3" t="s">
+        <v>1542</v>
       </c>
       <c r="J1270" s="4" t="s">
         <v>1473</v>
@@ -51445,8 +51619,8 @@
       <c r="F1271" s="3" t="s">
         <v>1518</v>
       </c>
-      <c r="G1271" s="14" t="s">
-        <v>1527</v>
+      <c r="G1271" s="3" t="s">
+        <v>1542</v>
       </c>
       <c r="J1271" s="4" t="s">
         <v>1473</v>
@@ -51569,7 +51743,7 @@
         <v>1438</v>
       </c>
       <c r="F1274" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="J1274" s="4" t="s">
         <v>1473</v>
@@ -51608,10 +51782,10 @@
         <v>1438</v>
       </c>
       <c r="F1275" s="3" t="s">
-        <v>1518</v>
-      </c>
-      <c r="G1275" s="14" t="s">
-        <v>1527</v>
+        <v>1537</v>
+      </c>
+      <c r="G1275" s="3" t="s">
+        <v>1542</v>
       </c>
       <c r="J1275" s="4" t="s">
         <v>1473</v>
@@ -51720,8 +51894,8 @@
       <c r="F1278" s="3" t="s">
         <v>1518</v>
       </c>
-      <c r="G1278" s="14" t="s">
-        <v>1527</v>
+      <c r="G1278" s="3" t="s">
+        <v>1542</v>
       </c>
       <c r="J1278" s="4" t="s">
         <v>1473</v>
@@ -59349,6 +59523,7 @@
   <autoFilter ref="A1:V1501" xr:uid="{2AA17C33-33CC-BA49-A564-8D59C07CF723}">
     <filterColumn colId="9">
       <filters>
+        <filter val="used"/>
         <filter val="yes"/>
       </filters>
     </filterColumn>
@@ -59357,24 +59532,55 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A2:T826 E827:T939 A827:D5000 E940:F940 H940:T940 E941:T1269 E1270:F1271 H1270:T1271 E1272:T1274 E1275:F1275 H1275:T1275 E1276:T1277 E1278:F1278 H1278:T1278 E1279:T5000">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="E827:T939 A827:D5000 E940:F940 H940:T940 E941:T1269 E1270:F1271 H1270:T1271 A2:T826 E1272:T5000">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+      <formula>$J2="no"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
       <formula>$J2="?"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
       <formula>$J2="yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$J2="no"</formula>
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+      <formula>$J2="used"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1270">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+      <formula>$J1270="no"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+      <formula>$J1270="?"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+      <formula>$J1270="yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+      <formula>$J1270="used"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1271">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+      <formula>$J1271="no"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>$J1271="?"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+      <formula>$J1271="yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>$J1271="used"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DA46B003-2126-4747-A49E-F0E3E0014219}">
           <x14:formula1>
-            <xm:f>_internal!$A$2:$A$4</xm:f>
+            <xm:f>_internal!$A$2:$A$5</xm:f>
           </x14:formula1>
           <xm:sqref>J2:J1048576</xm:sqref>
         </x14:dataValidation>
@@ -59389,12 +59595,6 @@
             <xm:f>_internal!$G$2:$G$3</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B1048576 D2:D1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E5CBCEDA-1269-E144-83F8-6C7CA2181620}">
-          <x14:formula1>
-            <xm:f>_internal!$E$2:$E$12</xm:f>
-          </x14:formula1>
-          <xm:sqref>G515</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BCC29FEE-9DA2-DB41-88E0-24F681167EAA}">
           <x14:formula1>
@@ -59541,10 +59741,10 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>1534</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -59626,7 +59826,7 @@
         <v>1502</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -59637,7 +59837,7 @@
         <v>1481</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -59648,7 +59848,7 @@
         <v>1438</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>1498</v>
@@ -59662,12 +59862,15 @@
         <v>1516</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>1539</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>1462</v>
@@ -59710,12 +59913,12 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E13" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E14" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
   </sheetData>
